--- a/r5-TC-FHIR-AG-Scheduling-R5-interation-documentation/StructureDefinition-at-scheduling-slot.xlsx
+++ b/r5-TC-FHIR-AG-Scheduling-R5-interation-documentation/StructureDefinition-at-scheduling-slot.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-07T16:14:22+00:00</t>
+    <t>2025-03-08T14:41:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-TC-FHIR-AG-Scheduling-R5-interation-documentation/StructureDefinition-at-scheduling-slot.xlsx
+++ b/r5-TC-FHIR-AG-Scheduling-R5-interation-documentation/StructureDefinition-at-scheduling-slot.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-08T14:41:39+00:00</t>
+    <t>2025-03-08T14:51:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
